--- a/fundraising_order_forms/023_steepted_tea_order_form--fundraising_order_forms.xlsx
+++ b/fundraising_order_forms/023_steepted_tea_order_form--fundraising_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>customer_preferences</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steepted Tea Order Form</t>
+          <t>What type of tea do you prefer?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>food_allergies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Do you have any food allergies?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>tea_drinking_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How often do you drink tea?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>What is your contact email address?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Do you have any special requests?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>tea_bags_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How many tea bags do you need?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your preferred method of payment?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>newsletter_subscription</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Do you want to join our newsletter?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>order_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your order date?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your contact phone number?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,62 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>loyalty_membership</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Are you a member of our loyalty program?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,272 +827,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>customer_preferences_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fundraising_order_forms</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fundraising Order Forms</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>customer_preferences_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>donation_forms</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Donation Forms</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>customer_preferences_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>herbal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Order Forms</t>
+          <t>Herbal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>customer_preferences_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_submit_choices</t>
+          <t>tea_drinking_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>tea_drinking_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fundraising_order_forms</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fundraising Order Forms</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>tea_drinking_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>donation_forms</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Donation Forms</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Order Forms</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>loyalty_membership_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>loyalty_membership_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
